--- a/public/samples/course_feilds.xlsx
+++ b/public/samples/course_feilds.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextSAAS\agencies\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A167C97-31AC-4BB6-AE6B-7BACA633CD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A327287-B3B8-4F40-A4C6-2609D14371D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Courses Import Template" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>university</t>
   </si>
@@ -152,51 +152,6 @@
   </si>
   <si>
     <t>intake_5_deadline</t>
-  </si>
-  <si>
-    <t>Harvard University</t>
-  </si>
-  <si>
-    <t>Masters</t>
-  </si>
-  <si>
-    <t>Computer Science</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>years</t>
-  </si>
-  <si>
-    <t>https://example.com/tuition</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>This program focuses on advanced computer science topics.</t>
-  </si>
-  <si>
-    <t>Bachelor's degree in related field.</t>
-  </si>
-  <si>
-    <t>WES evaluation required.</t>
-  </si>
-  <si>
-    <t>Fall 2025</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>AAAAAMS in Computer Science</t>
   </si>
 </sst>
 </file>
@@ -536,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:AR1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
@@ -673,92 +628,6 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2">
-        <v>45000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-      <c r="M2">
-        <v>310</v>
-      </c>
-      <c r="N2">
-        <v>650</v>
-      </c>
-      <c r="O2">
-        <v>7</v>
-      </c>
-      <c r="P2">
-        <v>100</v>
-      </c>
-      <c r="Q2">
-        <v>65</v>
-      </c>
-      <c r="R2">
-        <v>1200</v>
-      </c>
-      <c r="S2">
-        <v>25</v>
-      </c>
-      <c r="T2">
-        <v>110</v>
-      </c>
-      <c r="U2">
-        <v>3.5</v>
-      </c>
-      <c r="V2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" t="s">
-        <v>52</v>
-      </c>
-      <c r="X2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>57</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
